--- a/data/sistema/procesada/tarjeta/tarjeta_metadata_unida.xlsx
+++ b/data/sistema/procesada/tarjeta/tarjeta_metadata_unida.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q31"/>
+  <dimension ref="A1:Q32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2267,6 +2267,63 @@
         <v>1</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>BANCO PICHINCHA</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>3067XXXXXX5647</t>
+        </is>
+      </c>
+      <c r="C32" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="n">
+        <v>199.74</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>496.85</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>314.47</v>
+      </c>
+      <c r="J32" t="n">
+        <v>38</v>
+      </c>
+      <c r="K32" s="1" t="n">
+        <v>46208</v>
+      </c>
+      <c r="L32" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="M32" t="n">
+        <v>322.11</v>
+      </c>
+      <c r="N32" t="n">
+        <v>818.96</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Agosto2026.pdf</t>
+        </is>
+      </c>
+      <c r="P32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/sistema/procesada/tarjeta/tarjeta_metadata_unida.xlsx
+++ b/data/sistema/procesada/tarjeta/tarjeta_metadata_unida.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q32"/>
+  <dimension ref="A1:Q33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2324,6 +2324,63 @@
         <v>1</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>BANCO PICHINCHA</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>3067XXXXXX5647</t>
+        </is>
+      </c>
+      <c r="C33" s="1" t="n">
+        <v>46271</v>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="n">
+        <v>496.85</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1429.51</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1420.17</v>
+      </c>
+      <c r="J33" t="n">
+        <v>111</v>
+      </c>
+      <c r="K33" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="L33" s="1" t="n">
+        <v>46271</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1429.51</v>
+      </c>
+      <c r="N33" t="n">
+        <v>2859.02</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Septiembre26.pdf</t>
+        </is>
+      </c>
+      <c r="P33" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
